--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/07_Avaliacao_do_Governo_por_Sexo.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/07_Avaliacao_do_Governo_por_Sexo.xlsx
@@ -17,7 +17,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodologia" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Linhas_publicadas" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Suavizados_Mulheres'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'IC_Baixo_Mulheres'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IC_Alto_Mulheres'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Suavizados_Homens'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IC_Baixo_Homens'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'IC_Alto_Homens'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cobertura'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Metodologia'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Linhas_publicadas'!$A$1:$R$33</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -28,7 +38,7 @@
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,16 +49,25 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -62,17 +81,35 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,203 +475,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Ótimo/Bom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ruim/Péssimo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B2" t="n">
         <v>24</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>35</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B3" t="n">
         <v>30</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>32</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>26.50922152981643</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>33.93932137232421</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B5" t="n">
         <v>20</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>36</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>25.12445848390518</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>32.79721344755926</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="6" t="n">
         <v>39.35944268951185</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>45865</v>
+      </c>
+      <c r="B7" t="n">
         <v>21</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>38</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>32</v>
+      <c r="A8" s="5" t="n">
+        <v>45908</v>
       </c>
       <c r="B8" t="n">
         <v>32</v>
       </c>
       <c r="C8" t="n">
+        <v>32</v>
+      </c>
+      <c r="D8" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>28.42062176306051</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>32.89484455923487</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="6" t="n">
         <v>36.78968911846974</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B10" t="n">
         <v>31</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>30</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>27.09491348507648</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" s="6" t="n">
         <v>31.95254325746176</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="6" t="n">
         <v>37.56203460596941</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="5" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B12" t="n">
         <v>23</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>32</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B13" t="n">
         <v>33</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>26</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>37</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>29.29294767595231</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" s="6" t="n">
         <v>24.35242118931214</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="6" t="n">
         <v>43.59031524275146</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" t="n">
         <v>32</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>29</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="5" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>34.72874676901665</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" s="6" t="n">
         <v>23.93232742896908</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="6" t="n">
         <v>38.33892580201427</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>36.22378492972631</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" s="6" t="n">
         <v>19.80297790383631</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" s="6" t="n">
         <v>41.98426391946624</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -645,203 +742,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Ótimo/Bom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ruim/Péssimo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>19.16718822735457</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>29.60268004250284</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="6" t="n">
         <v>31.53665532509678</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>27.20682935590077</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>29.1567354703576</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="6" t="n">
         <v>34.05721212211379</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>24.03551502371925</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>31.19714546266292</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="6" t="n">
         <v>34.21875845189203</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>15.47365706369531</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>30.56838847643438</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" s="6" t="n">
         <v>34.45638470260129</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>22.73090828356563</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>30.1360469864331</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="6" t="n">
         <v>36.60126549722386</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>45865</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>16.39095809539135</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>32.50743624477744</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" s="6" t="n">
         <v>31.53665532509678</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>29.1567354703576</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>29.1567354703576</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" s="6" t="n">
         <v>32.09277581973586</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>25.74779422883483</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>30.02768227605195</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="6" t="n">
         <v>33.84367856275743</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>28.17828183055502</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>27.20412410524817</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" s="6" t="n">
         <v>33.07147133225083</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>24.60547764827457</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" s="6" t="n">
         <v>29.24215071210932</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="6" t="n">
         <v>34.75625453767643</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="5" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>18.23791937228789</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" s="6" t="n">
         <v>26.72142241576691</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" s="6" t="n">
         <v>35.43448448411737</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>30.14086482506321</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" s="6" t="n">
         <v>23.33287818812133</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" s="6" t="n">
         <v>34.06430147926317</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>26.68720855568484</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" s="6" t="n">
         <v>21.8648023545988</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="6" t="n">
         <v>40.69336095110953</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="6" t="n">
         <v>29.17038540291495</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" s="6" t="n">
         <v>26.24750831937233</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" s="6" t="n">
         <v>33.08835060060794</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="5" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>31.97009071916476</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" s="6" t="n">
         <v>21.60081268371714</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="6" t="n">
         <v>35.52886326698875</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>33.60893141328319</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" s="6" t="n">
         <v>17.8251265285948</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" s="6" t="n">
         <v>39.31314076393452</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -852,203 +1009,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Ótimo/Bom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ruim/Péssimo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>28.83281177264543</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>40.39731995749716</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="6" t="n">
         <v>42.46334467490322</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>32.79317064409923</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>34.8432645296424</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="6" t="n">
         <v>39.94278787788621</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>28.98292803591361</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>36.6814972819855</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="6" t="n">
         <v>39.78124154810797</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>24.52634293630469</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>41.43161152356562</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" s="6" t="n">
         <v>45.54361529739871</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>27.51800868424472</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>35.45837990868542</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="6" t="n">
         <v>42.11761988179985</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>45865</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>25.60904190460865</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>43.49256375522256</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" s="6" t="n">
         <v>42.46334467490322</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>34.8432645296424</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>34.8432645296424</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" s="6" t="n">
         <v>37.90722418026414</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>31.09344929728619</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>35.76200684241778</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="6" t="n">
         <v>39.73569967418204</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>33.82171816944498</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>32.79587589475182</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" s="6" t="n">
         <v>38.92852866774917</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>29.58434932187838</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" s="6" t="n">
         <v>34.6629358028142</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="6" t="n">
         <v>40.36781467426239</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="5" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>27.76208062771211</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" s="6" t="n">
         <v>37.27857758423309</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" s="6" t="n">
         <v>46.56551551588263</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>35.85913517493679</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" s="6" t="n">
         <v>28.66712181187867</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" s="6" t="n">
         <v>39.93569852073683</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>31.89868679621977</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" s="6" t="n">
         <v>26.84004002402547</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="6" t="n">
         <v>46.48726953439338</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="6" t="n">
         <v>34.82961459708505</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" s="6" t="n">
         <v>31.75249168062767</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" s="6" t="n">
         <v>38.91164939939206</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="5" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>37.48740281886855</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" s="6" t="n">
         <v>26.26384217422102</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="6" t="n">
         <v>41.1489883370398</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>38.83863844616944</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" s="6" t="n">
         <v>21.78082927907783</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" s="6" t="n">
         <v>44.65538707499795</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1059,203 +1276,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Ótimo/Bom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ruim/Péssimo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B2" t="n">
         <v>24</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" t="n">
         <v>31</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B3" t="n">
         <v>25</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" t="n">
         <v>28</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>23.82427095115527</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>28.78381936589648</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="6" t="n">
         <v>45.60809031705175</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B5" t="n">
         <v>21</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" t="n">
         <v>29</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>22.27395932990282</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>27.72604067009718</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>45865</v>
+      </c>
+      <c r="B7" t="n">
         <v>22</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" t="n">
         <v>30</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>29</v>
+      <c r="A8" s="5" t="n">
+        <v>45908</v>
       </c>
       <c r="B8" t="n">
         <v>29</v>
       </c>
       <c r="C8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D8" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>26.29021659982659</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" t="n">
         <v>29</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="6" t="n">
         <v>43.70978340017341</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B10" t="n">
         <v>29</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" t="n">
         <v>28</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>25.84540204359214</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" s="6" t="n">
         <v>28.78864948910196</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="6" t="n">
         <v>43.97162372275491</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="5" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B12" t="n">
         <v>22</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" t="n">
         <v>29</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B13" t="n">
         <v>33</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" t="n">
         <v>21</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>30.91685641299787</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" s="6" t="n">
         <v>21.41662871740042</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="6" t="n">
         <v>45.49977230440255</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" t="n">
         <v>31</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" t="n">
         <v>27</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>40</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="5" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>30.60493020021417</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" s="6" t="n">
         <v>22.25916240257012</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="6" t="n">
         <v>45.1359073972157</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>33.93193533829591</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" s="6" t="n">
         <v>18.80171828578565</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" s="6" t="n">
         <v>45.94630728146335</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1266,203 +1543,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Ótimo/Bom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ruim/Péssimo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>19.16718822735457</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>25.76649243895176</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="6" t="n">
         <v>38.38295613506229</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>22.26938693495863</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>25.16857676444515</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="6" t="n">
         <v>42.85706554832921</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>21.34797313731821</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>26.12024755661645</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="6" t="n">
         <v>42.68913147912171</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>16.39095809539135</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>23.86529335086245</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" s="6" t="n">
         <v>42.3465994845425</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>19.89736776752325</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>25.14827448788782</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="6" t="n">
         <v>45.13176508854066</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>45865</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>17.31244792515642</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>24.81442271826377</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" s="6" t="n">
         <v>40.36020576303113</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>26.13853985646985</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>26.13853985646985</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" s="6" t="n">
         <v>37.89845946124854</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>23.62794175888891</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>26.20001631923963</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="6" t="n">
         <v>40.6440525800963</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>26.14149743880386</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>25.17150330087115</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" s="6" t="n">
         <v>38.8907971698755</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>23.33529409204683</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" s="6" t="n">
         <v>26.12104805374646</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="6" t="n">
         <v>41.0551131856555</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="5" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>17.31244792515642</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" s="6" t="n">
         <v>23.86529335086245</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" s="6" t="n">
         <v>43.34320302853443</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>30.02709679999813</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" s="6" t="n">
         <v>18.42480814419477</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" s="6" t="n">
         <v>39.86990115126827</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>28.18030673336951</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" s="6" t="n">
         <v>18.95269459631749</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="6" t="n">
         <v>42.51837282522662</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="6" t="n">
         <v>28.06826617883122</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" s="6" t="n">
         <v>24.18575141096099</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" s="6" t="n">
         <v>36.89454839429388</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="5" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>27.89526041897183</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" s="6" t="n">
         <v>19.92540083869091</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="6" t="n">
         <v>42.21913809199398</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>31.32712948438921</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" s="6" t="n">
         <v>16.81046489139591</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" s="6" t="n">
         <v>43.22149122511178</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1473,203 +1810,263 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Ótimo/Bom</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Regular</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Ruim/Péssimo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="5" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B2" s="6" t="n">
         <v>28.83281177264543</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C2" s="6" t="n">
         <v>36.23350756104824</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" s="6" t="n">
         <v>49.61704386493771</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="5" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>27.73061306504137</v>
       </c>
-      <c r="B3" t="n">
+      <c r="C3" s="6" t="n">
         <v>30.83142323555485</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" s="6" t="n">
         <v>49.14293445167079</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="5" t="n">
+        <v>45733</v>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>26.30056876499232</v>
       </c>
-      <c r="B4" t="n">
+      <c r="C4" s="6" t="n">
         <v>31.44739117517652</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" s="6" t="n">
         <v>48.5270491549818</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="5" t="n">
+        <v>45810</v>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>25.60904190460865</v>
       </c>
-      <c r="B5" t="n">
+      <c r="C5" s="6" t="n">
         <v>34.13470664913755</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" s="6" t="n">
         <v>53.6534005154575</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="5" t="n">
+        <v>45817</v>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>24.65055089228238</v>
       </c>
-      <c r="B6" t="n">
+      <c r="C6" s="6" t="n">
         <v>30.30380685230655</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" s="6" t="n">
         <v>50.86823491145934</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="5" t="n">
+        <v>45865</v>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>26.68755207484358</v>
       </c>
-      <c r="B7" t="n">
+      <c r="C7" s="6" t="n">
         <v>35.18557728173623</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" s="6" t="n">
         <v>51.63979423696887</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="5" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>31.86146014353015</v>
       </c>
-      <c r="B8" t="n">
+      <c r="C8" s="6" t="n">
         <v>31.86146014353015</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" s="6" t="n">
         <v>44.10154053875146</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="5" t="n">
+        <v>45929</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>28.95249144076426</v>
       </c>
-      <c r="B9" t="n">
+      <c r="C9" s="6" t="n">
         <v>31.79998368076037</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" s="6" t="n">
         <v>46.77551422025051</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="5" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>31.85850256119614</v>
       </c>
-      <c r="B10" t="n">
+      <c r="C10" s="6" t="n">
         <v>30.82849669912885</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" s="6" t="n">
         <v>45.1092028301245</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="5" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>28.35550999513744</v>
       </c>
-      <c r="B11" t="n">
+      <c r="C11" s="6" t="n">
         <v>31.45625092445747</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" s="6" t="n">
         <v>46.88813425985433</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="5" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>26.68755207484358</v>
       </c>
-      <c r="B12" t="n">
+      <c r="C12" s="6" t="n">
         <v>34.13470664913755</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" s="6" t="n">
         <v>54.65679697146557</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="5" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>35.97290320000187</v>
       </c>
-      <c r="B13" t="n">
+      <c r="C13" s="6" t="n">
         <v>23.57519185580523</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" s="6" t="n">
         <v>46.13009884873173</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>33.65340609262624</v>
       </c>
-      <c r="B14" t="n">
+      <c r="C14" s="6" t="n">
         <v>23.88056283848335</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" s="6" t="n">
         <v>48.48117178357847</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B15" s="6" t="n">
         <v>33.93173382116878</v>
       </c>
-      <c r="B15" t="n">
+      <c r="C15" s="6" t="n">
         <v>29.81424858903901</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" s="6" t="n">
         <v>43.10545160570612</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="5" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>33.31459998145651</v>
       </c>
-      <c r="B16" t="n">
+      <c r="C16" s="6" t="n">
         <v>24.59292396644933</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" s="6" t="n">
         <v>48.05267670243742</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>36.53674119220261</v>
       </c>
-      <c r="B17" t="n">
+      <c r="C17" s="6" t="n">
         <v>20.79297168017539</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" s="6" t="n">
         <v>48.67112333781493</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1680,79 +2077,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>observacoes_publicadas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>primeira_data</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>ultima_data</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>numero_institutos</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>institutos</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>amostras_segmento_publicadas</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>fallbacks_amostra_segmento</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mulheres</t>
+          <t>Homens</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="7" t="n">
         <v>45684</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="7" t="n">
         <v>46203</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>Atlas, Ipec, PoderData</t>
         </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Homens</t>
+          <t>Mulheres</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>16</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="7" t="n">
         <v>45684</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="7" t="n">
         <v>46203</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Atlas, Ipec, PoderData</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1763,16 +2204,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>descricao</t>
         </is>
@@ -1784,7 +2229,7 @@
           <t>Universo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>Brasil, abertura publicada de sexo.</t>
         </is>
@@ -1796,7 +2241,7 @@
           <t>Grupos</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Rótulos FEM/Feminino e MAS/Masculino são harmonizados como Mulheres e Homens.</t>
         </is>
@@ -1805,28 +2250,41 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amostra e IC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Usa amostra do segmento quando publicada; na ausência, o código aplica o fallback conservador já usado para aberturas.</t>
+          <t>Cobertura mínima</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Exige Mulheres e Homens com ao menos duas datas publicadas em cada grupo.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Amostra e faixa</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Usa amostra do segmento quando publicada; na ausência, aplica fallback conservador. A faixa é somente amostral e aproximada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Interpretação</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>As curvas são agregados de pesquisas disponíveis; não são previsão eleitoral.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1837,98 +2295,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>data_referencia</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>instituto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>tipo_pesquisa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>frequencia_original</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>amostra_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>margem_erro_pp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>nivel_confianca_pct</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>nivel_geografico</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>geografia</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>segmento_tipo</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>segmento</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>amostra_segmento</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>otimo_bom_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>regular_pct</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>ruim_pessimo_pct</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>_linha_excel</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>peso_legacy</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>grupo_abertura</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="7" t="n">
         <v>45684</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1985,16 +2468,19 @@
         <v>44</v>
       </c>
       <c r="P2" t="n">
+        <v>878</v>
+      </c>
+      <c r="Q2" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="7" t="n">
         <v>45684</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -2051,16 +2537,19 @@
         <v>37</v>
       </c>
       <c r="P3" t="n">
+        <v>877</v>
+      </c>
+      <c r="Q3" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="7" t="n">
         <v>45727</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -2120,16 +2609,19 @@
         <v>46</v>
       </c>
       <c r="P4" t="n">
+        <v>961</v>
+      </c>
+      <c r="Q4" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="7" t="n">
         <v>45727</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -2189,16 +2681,19 @@
         <v>37</v>
       </c>
       <c r="P5" t="n">
+        <v>960</v>
+      </c>
+      <c r="Q5" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="7" t="n">
         <v>45733</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -2255,16 +2750,19 @@
         <v>45</v>
       </c>
       <c r="P6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Q6" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="7" t="n">
         <v>45733</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -2321,16 +2819,19 @@
         <v>37</v>
       </c>
       <c r="P7" t="n">
+        <v>998</v>
+      </c>
+      <c r="Q7" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="7" t="n">
         <v>45810</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -2387,16 +2888,19 @@
         <v>48</v>
       </c>
       <c r="P8" t="n">
+        <v>1117</v>
+      </c>
+      <c r="Q8" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="7" t="n">
         <v>45810</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -2453,16 +2957,19 @@
         <v>40</v>
       </c>
       <c r="P9" t="n">
+        <v>1116</v>
+      </c>
+      <c r="Q9" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="7" t="n">
         <v>45817</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -2522,16 +3029,19 @@
         <v>48</v>
       </c>
       <c r="P10" t="n">
+        <v>1160</v>
+      </c>
+      <c r="Q10" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="7" t="n">
         <v>45817</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -2591,16 +3101,19 @@
         <v>39</v>
       </c>
       <c r="P11" t="n">
+        <v>1159</v>
+      </c>
+      <c r="Q11" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="7" t="n">
         <v>45865</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -2657,16 +3170,19 @@
         <v>46</v>
       </c>
       <c r="P12" t="n">
+        <v>1244</v>
+      </c>
+      <c r="Q12" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="7" t="n">
         <v>45865</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -2723,16 +3239,19 @@
         <v>37</v>
       </c>
       <c r="P13" t="n">
+        <v>1243</v>
+      </c>
+      <c r="Q13" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="7" t="n">
         <v>45908</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2792,16 +3311,19 @@
         <v>41</v>
       </c>
       <c r="P14" t="n">
+        <v>1328</v>
+      </c>
+      <c r="Q14" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="7" t="n">
         <v>45908</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2861,16 +3383,19 @@
         <v>35</v>
       </c>
       <c r="P15" t="n">
+        <v>1327</v>
+      </c>
+      <c r="Q15" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="7" t="n">
         <v>45929</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2927,16 +3452,19 @@
         <v>47</v>
       </c>
       <c r="P16" t="n">
+        <v>1382</v>
+      </c>
+      <c r="Q16" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="7" t="n">
         <v>45929</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2993,16 +3521,19 @@
         <v>39</v>
       </c>
       <c r="P17" t="n">
+        <v>1381</v>
+      </c>
+      <c r="Q17" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="7" t="n">
         <v>45999</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -3062,16 +3593,19 @@
         <v>42</v>
       </c>
       <c r="P18" t="n">
+        <v>1499</v>
+      </c>
+      <c r="Q18" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="7" t="n">
         <v>45999</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -3131,16 +3665,19 @@
         <v>36</v>
       </c>
       <c r="P19" t="n">
+        <v>1498</v>
+      </c>
+      <c r="Q19" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="7" t="n">
         <v>46006</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -3197,16 +3734,19 @@
         <v>47</v>
       </c>
       <c r="P20" t="n">
+        <v>1534</v>
+      </c>
+      <c r="Q20" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="7" t="n">
         <v>46006</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -3263,16 +3803,19 @@
         <v>40</v>
       </c>
       <c r="P21" t="n">
+        <v>1533</v>
+      </c>
+      <c r="Q21" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="7" t="n">
         <v>46048</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -3329,16 +3872,19 @@
         <v>49</v>
       </c>
       <c r="P22" t="n">
+        <v>1606</v>
+      </c>
+      <c r="Q22" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="7" t="n">
         <v>46048</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -3395,16 +3941,19 @@
         <v>41</v>
       </c>
       <c r="P23" t="n">
+        <v>1605</v>
+      </c>
+      <c r="Q23" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="7" t="n">
         <v>46090</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3464,16 +4013,19 @@
         <v>43</v>
       </c>
       <c r="P24" t="n">
+        <v>1689</v>
+      </c>
+      <c r="Q24" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="7" t="n">
         <v>46090</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3533,16 +4085,19 @@
         <v>37</v>
       </c>
       <c r="P25" t="n">
+        <v>1688</v>
+      </c>
+      <c r="Q25" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="7" t="n">
         <v>46104</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3599,16 +4154,19 @@
         <v>49</v>
       </c>
       <c r="P26" t="n">
+        <v>1730</v>
+      </c>
+      <c r="Q26" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="7" t="n">
         <v>46104</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3665,16 +4223,19 @@
         <v>53</v>
       </c>
       <c r="P27" t="n">
+        <v>1729</v>
+      </c>
+      <c r="Q27" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="7" t="n">
         <v>46190</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -3734,16 +4295,19 @@
         <v>40</v>
       </c>
       <c r="P28" t="n">
+        <v>1803</v>
+      </c>
+      <c r="Q28" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="7" t="n">
         <v>46190</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -3803,16 +4367,19 @@
         <v>36</v>
       </c>
       <c r="P29" t="n">
+        <v>1802</v>
+      </c>
+      <c r="Q29" s="6" t="n">
         <v>0.8776119402985074</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="7" t="n">
         <v>46197</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -3869,16 +4436,19 @@
         <v>53</v>
       </c>
       <c r="P30" t="n">
+        <v>1821</v>
+      </c>
+      <c r="Q30" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="7" t="n">
         <v>46197</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -3935,16 +4505,19 @@
         <v>42</v>
       </c>
       <c r="P31" t="n">
+        <v>1820</v>
+      </c>
+      <c r="Q31" s="6" t="n">
         <v>0.5850746268656717</v>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="7" t="n">
         <v>46203</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -3991,26 +4564,29 @@
           <t>Masculino</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="6" t="n">
         <v>40.4</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32" s="6" t="n">
         <v>12.2</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="6" t="n">
         <v>47.4</v>
       </c>
       <c r="P32" t="n">
+        <v>1842</v>
+      </c>
+      <c r="Q32" s="6" t="n">
         <v>0.8686567164179104</v>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>Homens</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="7" t="n">
         <v>46203</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -4057,25 +4633,29 @@
           <t>Feminino</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="6" t="n">
         <v>39.1</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33" s="6" t="n">
         <v>11.8</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="6" t="n">
         <v>49.1</v>
       </c>
       <c r="P33" t="n">
+        <v>1841</v>
+      </c>
+      <c r="Q33" s="6" t="n">
         <v>0.8686567164179104</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>Mulheres</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>